--- a/artfynd/A 50775-2025 artfynd.xlsx
+++ b/artfynd/A 50775-2025 artfynd.xlsx
@@ -1891,12 +1891,7 @@
         <v>93958515</v>
       </c>
       <c r="B12" t="n">
-        <v>57000</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58581</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,10 +1939,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>413518.2650777227</v>
+        <v>413518</v>
       </c>
       <c r="R12" t="n">
-        <v>6446671.674860728</v>
+        <v>6446672</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 50775-2025 artfynd.xlsx
+++ b/artfynd/A 50775-2025 artfynd.xlsx
@@ -1891,7 +1891,7 @@
         <v>93958515</v>
       </c>
       <c r="B12" t="n">
-        <v>58581</v>
+        <v>58582</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 50775-2025 artfynd.xlsx
+++ b/artfynd/A 50775-2025 artfynd.xlsx
@@ -1891,7 +1891,7 @@
         <v>93958515</v>
       </c>
       <c r="B12" t="n">
-        <v>58582</v>
+        <v>58586</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 50775-2025 artfynd.xlsx
+++ b/artfynd/A 50775-2025 artfynd.xlsx
@@ -1891,7 +1891,7 @@
         <v>93958515</v>
       </c>
       <c r="B12" t="n">
-        <v>58586</v>
+        <v>58587</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 50775-2025 artfynd.xlsx
+++ b/artfynd/A 50775-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4153,6 +4153,298 @@
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134145366</v>
+      </c>
+      <c r="B31" t="n">
+        <v>56905</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100088</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vanlig snok</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Natrix natrix</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Falevi, Vg</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>413940</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6446573</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134145363</v>
+      </c>
+      <c r="B32" t="n">
+        <v>103455</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Falevi, Vg</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>413493</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6446678</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Luttra</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134145364</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58124</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Falevi, Vg</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>413614</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6446582</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Luttra</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50775-2025 artfynd.xlsx
+++ b/artfynd/A 50775-2025 artfynd.xlsx
@@ -4158,7 +4158,7 @@
         <v>134145366</v>
       </c>
       <c r="B31" t="n">
-        <v>56905</v>
+        <v>56915</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>134145363</v>
       </c>
       <c r="B32" t="n">
-        <v>103455</v>
+        <v>103465</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>134145364</v>
       </c>
       <c r="B33" t="n">
-        <v>58124</v>
+        <v>58134</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 50775-2025 artfynd.xlsx
+++ b/artfynd/A 50775-2025 artfynd.xlsx
@@ -4255,7 +4255,7 @@
         <v>134145363</v>
       </c>
       <c r="B32" t="n">
-        <v>103465</v>
+        <v>103467</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 50775-2025 artfynd.xlsx
+++ b/artfynd/A 50775-2025 artfynd.xlsx
@@ -4255,7 +4255,7 @@
         <v>134145363</v>
       </c>
       <c r="B32" t="n">
-        <v>103467</v>
+        <v>103468</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 50775-2025 artfynd.xlsx
+++ b/artfynd/A 50775-2025 artfynd.xlsx
@@ -4255,7 +4255,7 @@
         <v>134145363</v>
       </c>
       <c r="B32" t="n">
-        <v>103468</v>
+        <v>103475</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 50775-2025 artfynd.xlsx
+++ b/artfynd/A 50775-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2710933</v>
+        <v>104376810</v>
       </c>
       <c r="B2" t="n">
-        <v>95710</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220250</v>
+        <v>569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>SO om Hulesjön, infarten mot fd ladan, Vg</t>
+          <t>Falköpings mosse, S om Hulesjön, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>413492.2468604025</v>
+        <v>413441</v>
       </c>
       <c r="R2" t="n">
-        <v>6446691.246452452</v>
+        <v>6446683</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +752,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-01-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-01-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-29</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>3 plantor i tät lövskog på torv, ca 10m från spången och ca 10m från Mossvägen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,6 +771,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6981261</v>
+        <v>104408774</v>
       </c>
       <c r="B3" t="n">
-        <v>95710</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98215</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,34 +801,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220250</v>
+        <v>569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mossvägen, O vägkant S om Hulesjön, Vg</t>
+          <t>Hulesjön, S om, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>413484.1446863447</v>
+        <v>413443</v>
       </c>
       <c r="R3" t="n">
-        <v>6446683.504505682</v>
+        <v>6446683</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,27 +862,17 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Luttra</t>
+          <t>Falköping</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-06-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-06-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,86 +881,72 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Tät lövskog i torvmark</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jörgen Grahn</t>
+          <t>Ulf Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jörgen Grahn</t>
+          <t>Ulf Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>53897666</v>
+        <v>119339022</v>
       </c>
       <c r="B4" t="n">
-        <v>56698</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98215</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102122</v>
+        <v>569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flodsångare</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Locustella fluviatilis</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Wolf, 1810)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Väg 47  syd Hulesjön, Hulesjön, Falköping, Vg</t>
+          <t>Hulesjöns strandskog i S, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>413594.0814628213</v>
+        <v>413444</v>
       </c>
       <c r="R4" t="n">
-        <v>6446485.780293012</v>
+        <v>6446683</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,32 +965,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Luttra</t>
+          <t>Falköping</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-06-11</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>18:35</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-06-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>20:45</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Vid vägskyllten öster infarten till Hulesjön</t>
+          <t>de JoG hittade oktober 2022. En grupp om åtm 4 ex på en liten yta. Snitseln var kvar. Några meter på spången, sen 15 m till höger, bortom groparna som kanske är gamla torvhålor men inte på det låglänta närmre sjön. Udda, inte alls lik Dryopteris.  Svår att se pga få blad, mörkgröna och inte avvikande från vegetationen i övrigt. Långsmala bladskivor. En del blad helt uppräta, och småbladen då vinklade nittio grader så de bildade "hyllor". Foto. 2024-03-24 fanns gröna fjolårsblad, men det mesta hade vissnat och de gröna bladen var i dåligt skick: nedliggande och nedväxta.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,65 +995,69 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lennart  Ljuhs</t>
+          <t>Jörgen Grahn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lennart  Ljuhs, Ingvor Ljuhs</t>
+          <t>Jörgen Grahn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>68888719</v>
+        <v>560021</v>
       </c>
       <c r="B5" t="n">
-        <v>95710</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107868</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220250</v>
+        <v>1855</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Åkerkulla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Anthemis arvensis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hulesjön SO om, Vg</t>
+          <t>Mossvägen × Södra Tvärvägen, Falköping, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>413508.6913607907</v>
+        <v>413358</v>
       </c>
       <c r="R5" t="n">
-        <v>6446620.676301056</v>
+        <v>6446558</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,27 +1081,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-02-25</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-06-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-02-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-06-07</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Vändplats, vägdike och vägkant</t>
+          <t>1 planta (tregrenad) i Mossvägens östra vägkant strax intill korsningen (spridd med sädtransporter till Roséns?)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,12 +1106,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1156,12 +1121,7 @@
         <v>81215719</v>
       </c>
       <c r="B6" t="n">
-        <v>104790</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107868</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>413473.7873054951</v>
+        <v>413474</v>
       </c>
       <c r="R6" t="n">
-        <v>6446548.056559379</v>
+        <v>6446548</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1226,19 +1186,9 @@
           <t>2018-06-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2018-08-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1274,15 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>81215724</v>
+        <v>134145365</v>
       </c>
       <c r="B7" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,37 +1235,33 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>2558</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Krushättemossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Ulota crispa s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Falköpings kommun, Vg</t>
+          <t>Falevi, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>413722.2375511723</v>
+        <v>413426</v>
       </c>
       <c r="R7" t="n">
-        <v>6446493.023084844</v>
+        <v>6446599</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1344,27 +1285,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2018-06-15</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2018-08-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Observatör: Lennart Sundh. Naturvärdesinventering för Falköpings kommun. Calluna AB (JSN0108).</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,31 +1305,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Alfred Olofsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erik Edvardsson, Lennart Sundh</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering av kommunal mark i Falköpings kommun 2018-2019</t>
-        </is>
-      </c>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>81214840</v>
+        <v>93957925</v>
       </c>
       <c r="B8" t="n">
-        <v>56698</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ej möjlig att validera</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,37 +1328,53 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102122</v>
+        <v>100048</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Flodsångare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Locustella fluviatilis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Wolf, 1810)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Falköpings kommun, Vg</t>
+          <t>Hulesjön Parkering, Hulesjön, Falköping, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>413646.2640467414</v>
+        <v>413518</v>
       </c>
       <c r="R8" t="n">
-        <v>6446769.188522014</v>
+        <v>6446672</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1465,27 +1398,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2018-06-15</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2018-08-15</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Observatör: Lennart Sundh. Naturvärdesinventering för Falköpings kommun. Calluna AB (JSN0108).</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1500,53 +1428,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Lennart  Ljuhs</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Edvardsson, Lennart Sundh</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering av kommunal mark i Falköpings kommun 2018-2019</t>
-        </is>
-      </c>
+          <t>Lennart  Ljuhs</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>93958536</v>
+        <v>93958381</v>
       </c>
       <c r="B9" t="n">
-        <v>56812</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57890</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102999</v>
+        <v>100082</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1568,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>413518.2650777227</v>
+        <v>413518</v>
       </c>
       <c r="R9" t="n">
-        <v>6446671.674860728</v>
+        <v>6446672</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1640,32 +1559,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>93958620</v>
+        <v>134145366</v>
       </c>
       <c r="B10" t="n">
-        <v>56608</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56915</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102981</v>
+        <v>100088</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1673,32 +1587,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hulesjön Parkering, Hulesjön, Falköping, Vg</t>
+          <t>Falevi, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>413518.2650777227</v>
+        <v>413940</v>
       </c>
       <c r="R10" t="n">
-        <v>6446671.674860728</v>
+        <v>6446573</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1722,22 +1624,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>16:43</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>18:27</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1752,61 +1644,56 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lennart  Ljuhs</t>
+          <t>Alfred Olofsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lennart  Ljuhs</t>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>93958347</v>
+        <v>121641984</v>
       </c>
       <c r="B11" t="n">
-        <v>55946</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57903</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102963</v>
+        <v>102110</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1816,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>413518.2650777227</v>
+        <v>413518</v>
       </c>
       <c r="R11" t="n">
-        <v>6446671.674860728</v>
+        <v>6446672</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1846,22 +1733,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>16:43</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>18:27</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1888,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>93958515</v>
+        <v>53897666</v>
       </c>
       <c r="B12" t="n">
-        <v>58591</v>
+        <v>58195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1899,21 +1776,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103051</v>
+        <v>102122</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenfink</t>
+          <t>Flodsångare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carpodacus erythrinus</t>
+          <t>Locustella fluviatilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pallas, 1770)</t>
+          <t>(Wolf, 1810)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1921,31 +1798,30 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hulesjön Parkering, Hulesjön, Falköping, Vg</t>
+          <t>Väg 47  syd Hulesjön, Hulesjön, Falköping, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>413518</v>
+        <v>413594</v>
       </c>
       <c r="R12" t="n">
-        <v>6446672</v>
+        <v>6446486</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1964,27 +1840,32 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Falköping</t>
+          <t>Luttra</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2015-06-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2015-06-11</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Vid vägskyllten öster infarten till Hulesjön</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2004,72 +1885,55 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lennart  Ljuhs</t>
+          <t>Lennart  Ljuhs, Ingvor Ljuhs</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>93958611</v>
+        <v>81214840</v>
       </c>
       <c r="B13" t="n">
-        <v>55667</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102976</v>
+        <v>102122</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Flodsångare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Locustella fluviatilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>(Wolf, 1810)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hulesjön Parkering, Hulesjön, Falköping, Vg</t>
+          <t>Falköpings kommun, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>413518.2650777227</v>
+        <v>413646</v>
       </c>
       <c r="R13" t="n">
-        <v>6446671.674860728</v>
+        <v>6446769</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2093,22 +1957,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:43</t>
+          <t>2018-06-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>18:27</t>
+          <t>2018-08-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Observatör: Lennart Sundh. Naturvärdesinventering för Falköpings kommun. Calluna AB (JSN0108).</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2123,27 +1982,26 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lennart  Ljuhs</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lennart  Ljuhs</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Erik Edvardsson, Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering av kommunal mark i Falköpings kommun 2018-2019</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>93958340</v>
+        <v>93958347</v>
       </c>
       <c r="B14" t="n">
-        <v>56521</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57546</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,21 +2009,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103035</v>
+        <v>102963</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2187,10 +2045,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>413518.2650777227</v>
+        <v>413518</v>
       </c>
       <c r="R14" t="n">
-        <v>6446671.674860728</v>
+        <v>6446672</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2259,53 +2117,44 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>93958009</v>
+        <v>93958611</v>
       </c>
       <c r="B15" t="n">
-        <v>56859</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57774</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103018</v>
+        <v>102976</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>besöker bebott bo</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2315,10 +2164,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>413518.2650777227</v>
+        <v>413518</v>
       </c>
       <c r="R15" t="n">
-        <v>6446671.674860728</v>
+        <v>6446672</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2387,15 +2236,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>93958486</v>
+        <v>93958617</v>
       </c>
       <c r="B16" t="n">
-        <v>56887</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2403,37 +2247,33 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102995</v>
+        <v>102980</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2443,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>413518.2650777227</v>
+        <v>413518</v>
       </c>
       <c r="R16" t="n">
-        <v>6446671.674860728</v>
+        <v>6446672</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2515,32 +2355,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>93957983</v>
+        <v>93958620</v>
       </c>
       <c r="B17" t="n">
-        <v>56538</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58212</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103020</v>
+        <v>102981</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2550,14 +2385,14 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2567,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>413518.2650777227</v>
+        <v>413518</v>
       </c>
       <c r="R17" t="n">
-        <v>6446671.674860728</v>
+        <v>6446672</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2639,15 +2474,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>94341046</v>
+        <v>93958392</v>
       </c>
       <c r="B18" t="n">
-        <v>56717</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58541</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,33 +2485,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103008</v>
+        <v>102987</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2691,10 +2525,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>413518.2650777227</v>
+        <v>413518</v>
       </c>
       <c r="R18" t="n">
-        <v>6446671.674860728</v>
+        <v>6446672</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2721,22 +2555,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-06-19</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-06-19</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2763,15 +2597,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>94340991</v>
+        <v>93958329</v>
       </c>
       <c r="B19" t="n">
-        <v>56806</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2779,21 +2608,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103001</v>
+        <v>102990</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2805,7 +2634,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2815,10 +2644,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>413518.2650777227</v>
+        <v>413518</v>
       </c>
       <c r="R19" t="n">
-        <v>6446671.674860728</v>
+        <v>6446672</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2845,22 +2674,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-06-19</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-06-19</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2887,32 +2716,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>93957925</v>
+        <v>93958486</v>
       </c>
       <c r="B20" t="n">
-        <v>56401</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58463</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100048</v>
+        <v>102995</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2943,10 +2767,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>413518.2650777227</v>
+        <v>413518</v>
       </c>
       <c r="R20" t="n">
-        <v>6446671.674860728</v>
+        <v>6446672</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3015,54 +2839,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104408831</v>
+        <v>93958536</v>
       </c>
       <c r="B21" t="n">
-        <v>95710</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58393</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220250</v>
+        <v>102999</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hulesjön, SO om, Vg</t>
+          <t>Hulesjön Parkering, Hulesjön, Falköping, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>413491.040057439</v>
+        <v>413518</v>
       </c>
       <c r="R21" t="n">
-        <v>6446684.410008594</v>
+        <v>6446672</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3084,27 +2911,27 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Luttra</t>
+          <t>Falköping</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-10-31</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-10-31</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3113,39 +2940,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulf Persson</t>
+          <t>Lennart  Ljuhs</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulf Persson</t>
+          <t>Lennart  Ljuhs</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119338954</v>
+        <v>94340991</v>
       </c>
       <c r="B22" t="n">
-        <v>106934</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3153,34 +2969,46 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220107</v>
+        <v>103001</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Klofibbla</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crepis tectorum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mossvägen: O vägkant vid Hulesjön, Vg</t>
+          <t>Hulesjön Parkering, Hulesjön, Falköping, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>413563</v>
+        <v>413518</v>
       </c>
       <c r="R22" t="n">
-        <v>6446764</v>
+        <v>6446672</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3207,17 +3035,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2021-06-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>några blommande ex, bl a ett stort med rätt brett tunglika blad. Inte noga nycklad, men grönfibbla var det i alla fall inte.</t>
+          <t>2021-06-19</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3232,49 +3065,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jörgen Grahn</t>
+          <t>Lennart  Ljuhs</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jörgen Grahn</t>
+          <t>Lennart  Ljuhs</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121641984</v>
+        <v>65812268</v>
       </c>
       <c r="B23" t="n">
-        <v>57285</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58198</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102110</v>
+        <v>103003</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Gräshoppsångare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Locustella naevia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3286,20 +3114,19 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hulesjön Parkering, Hulesjön, Falköping, Vg</t>
+          <t>Hulesjön, Falköping, Hulesjön, Falköping, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>413518</v>
+        <v>413573</v>
       </c>
       <c r="R23" t="n">
-        <v>6446672</v>
+        <v>6446817</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3326,12 +3153,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2017-05-23</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2017-05-23</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3346,68 +3183,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lennart  Ljuhs</t>
+          <t>Fredrik Larsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lennart  Ljuhs</t>
+          <t>Fredrik Larsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122094811</v>
+        <v>81214827</v>
       </c>
       <c r="B24" t="n">
-        <v>58239</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58198</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>208249</v>
+        <v>103003</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gräshoppsångare</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Locustella naevia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Boddaert, 1783)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Falevi, Vg</t>
+          <t>Falköpings kommun, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>414008</v>
+        <v>414032</v>
       </c>
       <c r="R24" t="n">
-        <v>6446504</v>
+        <v>6446434</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3431,12 +3260,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2018-06-15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2018-08-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Observatör: Lennart Sundh. Naturvärdesinventering för Falköpings kommun. Calluna AB (JSN0108).</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3445,34 +3279,32 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Alfred Olofsson</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Erik Edvardsson, Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering av kommunal mark i Falköpings kommun 2018-2019</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122094809</v>
+        <v>94341046</v>
       </c>
       <c r="B25" t="n">
-        <v>58237</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58286</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,24 +3312,28 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>208250</v>
+        <v>103008</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ärtsångare</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
@@ -3508,14 +3344,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Falevi, Vg</t>
+          <t>Hulesjön Parkering, Hulesjön, Falköping, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>413977</v>
+        <v>413518</v>
       </c>
       <c r="R25" t="n">
-        <v>6446466</v>
+        <v>6446672</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3542,17 +3378,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2021-06-19</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Spel</t>
+          <t>2021-06-19</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3561,34 +3402,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Alfred Olofsson</t>
+          <t>Lennart  Ljuhs</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning</t>
+          <t>Lennart  Ljuhs</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122094808</v>
+        <v>93958009</v>
       </c>
       <c r="B26" t="n">
-        <v>58239</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3596,16 +3431,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>208249</v>
+        <v>103018</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3613,25 +3453,28 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>besöker bebott bo</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Falevi, Vg</t>
+          <t>Hulesjön Parkering, Hulesjön, Falköping, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>413975</v>
+        <v>413518</v>
       </c>
       <c r="R26" t="n">
-        <v>6446464</v>
+        <v>6446672</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3658,17 +3501,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Spel</t>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3677,77 +3525,75 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alfred Olofsson</t>
+          <t>Lennart  Ljuhs</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning</t>
+          <t>Lennart  Ljuhs</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122094804</v>
+        <v>93957983</v>
       </c>
       <c r="B27" t="n">
-        <v>58237</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>208250</v>
+        <v>103020</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Falevi, Vg</t>
+          <t>Hulesjön Parkering, Hulesjön, Falköping, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>413592</v>
+        <v>413518</v>
       </c>
       <c r="R27" t="n">
-        <v>6446763</v>
+        <v>6446672</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3774,17 +3620,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Spel</t>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3793,80 +3644,66 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alfred Olofsson</t>
+          <t>Lennart  Ljuhs</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning</t>
+          <t>Lennart  Ljuhs</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122094806</v>
+        <v>134145364</v>
       </c>
       <c r="B28" t="n">
-        <v>58237</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58134</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>208250</v>
+        <v>103020</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Falevi, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>413664</v>
+        <v>413614</v>
       </c>
       <c r="R28" t="n">
-        <v>6446577</v>
+        <v>6446582</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3885,22 +3722,17 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Falköping</t>
+          <t>Luttra</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Spel</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3909,7 +3741,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3921,49 +3752,52 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning</t>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122094810</v>
+        <v>93958515</v>
       </c>
       <c r="B29" t="n">
-        <v>58237</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58608</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>208250</v>
+        <v>103051</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Rosenfink</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Carpodacus erythrinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Pallas, 1770)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -3972,14 +3806,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Falevi, Vg</t>
+          <t>Hulesjön Parkering, Hulesjön, Falköping, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>414008</v>
+        <v>413518</v>
       </c>
       <c r="R29" t="n">
-        <v>6446504</v>
+        <v>6446672</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4006,17 +3840,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Spel samt 5 ägg klumpar</t>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4025,46 +3864,45 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alfred Olofsson</t>
+          <t>Lennart  Ljuhs</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning</t>
+          <t>Lennart  Ljuhs</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122094799</v>
+        <v>81215717</v>
       </c>
       <c r="B30" t="n">
-        <v>58211</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43258</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>208245</v>
+        <v>201129</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vitfläckig guldvinge</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lycaena virgaureae</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4072,28 +3910,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Falevi, Vg</t>
+          <t>Falköpings kommun, Vg</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>413601</v>
+        <v>413547</v>
       </c>
       <c r="R30" t="n">
-        <v>6446780</v>
+        <v>6446505</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4112,22 +3942,22 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Falköping</t>
+          <t>Luttra</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2018-06-15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2018-08-15</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>En synobs</t>
+          <t>Observatör: Lennart Sundh. Naturvärdesinventering för Falköpings kommun. Calluna AB (JSN0108).</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4136,46 +3966,49 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Alfred Olofsson</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Erik Edvardsson, Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering av kommunal mark i Falköpings kommun 2018-2019</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134145366</v>
+        <v>81215720</v>
       </c>
       <c r="B31" t="n">
-        <v>56915</v>
+        <v>43258</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100088</v>
+        <v>201129</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Lycaena virgaureae</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4186,17 +4019,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Falevi, Vg</t>
+          <t>Falköpings kommun, Vg</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>413940</v>
+        <v>413630</v>
       </c>
       <c r="R31" t="n">
-        <v>6446573</v>
+        <v>6446583</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4220,12 +4053,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2018-06-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2018-08-15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Observatör: Lennart Sundh. Naturvärdesinventering för Falköpings kommun. Calluna AB (JSN0108).</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4240,60 +4078,76 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alfred Olofsson</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Erik Edvardsson, Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering av kommunal mark i Falköpings kommun 2018-2019</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134145363</v>
+        <v>93958340</v>
       </c>
       <c r="B32" t="n">
-        <v>103475</v>
+        <v>58085</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>223246</v>
+        <v>205976</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Falevi, Vg</t>
+          <t>Hulesjön Parkering, Hulesjön, Falköping, Vg</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>413493</v>
+        <v>413518</v>
       </c>
       <c r="R32" t="n">
-        <v>6446678</v>
+        <v>6446672</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4312,17 +4166,27 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Luttra</t>
+          <t>Falköping</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4331,46 +4195,45 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alfred Olofsson</t>
+          <t>Lennart  Ljuhs</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+          <t>Lennart  Ljuhs</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134145364</v>
+        <v>122094793</v>
       </c>
       <c r="B33" t="n">
-        <v>58134</v>
+        <v>58790</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103020</v>
+        <v>208245</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4379,19 +4242,24 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Falevi, Vg</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>413614</v>
+        <v>413630</v>
       </c>
       <c r="R33" t="n">
-        <v>6446582</v>
+        <v>6446846</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4410,17 +4278,17 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Luttra</t>
+          <t>Falköping</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4429,6 +4297,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4444,6 +4313,2879 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>122094799</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Falevi, Vg</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>413601</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6446780</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>En synobs</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>122094801</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Falevi, Vg</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>413626</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6446808</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>122094808</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Falevi, Vg</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>413975</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6446464</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Spel</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>122094811</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Falevi, Vg</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>414008</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6446504</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>122094803</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58815</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Falevi, Vg</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>413617</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6446805</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Spel</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>122094804</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58815</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Falevi, Vg</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>413592</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6446763</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Spel</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>122094806</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58815</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Falevi, Vg</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>413664</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6446577</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Spel</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>122094809</v>
+      </c>
+      <c r="B41" t="n">
+        <v>58815</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Falevi, Vg</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>413977</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6446466</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Spel</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>122094810</v>
+      </c>
+      <c r="B42" t="n">
+        <v>58815</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Falevi, Vg</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>414008</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6446504</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Spel samt 5 ägg klumpar</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2244116</v>
+      </c>
+      <c r="B43" t="n">
+        <v>111405</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>219719</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Säfferot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Seseli libanotis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) W. D. J. Koch</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>norra vägskärningen av Södra Tvärvägen O om Mossvägen, Vg</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>413466</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6446513</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Luttra</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2010-08-21</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2010-08-21</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2 blommande och mycket småplantor i V</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>60510364</v>
+      </c>
+      <c r="B44" t="n">
+        <v>111405</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>219719</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Säfferot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Seseli libanotis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) W. D. J. Koch</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>N vägskärningen, S Tvärvägen O om Mossvägen, Vg</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>413476</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6446513</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Luttra</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2016-07-03</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2016-07-03</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>3--4 blommande långt upp mot åkern, i övrigt svaga sterila ex</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>118852342</v>
+      </c>
+      <c r="B45" t="n">
+        <v>111405</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>219719</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Säfferot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Seseli libanotis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) W. D. J. Koch</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Slänt v 47 Falevi, Falköping, Vg</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>413481</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6446522</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Luttra</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Dag Fredriksson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Dag Fredriksson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>6981254</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99026</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>219788</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Ängsnycklar</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Södra tvärvägen, N vägdiket och vägskärningen O om Mossvägen, Vg</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>413517</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6446494</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Luttra</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2013-06-14</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2013-06-14</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>ca 30 ex, en del mycket välväxta nere vid vägdiket.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>60510232</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99026</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>219788</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ängsnycklar</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>N vägskärningen, S Tvärvägen O om Mossvägen, Vg</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>413426</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6446533</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Luttra</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2016-06-25</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2016-06-25</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>1 ex</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>60510359</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99026</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>219788</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Ängsnycklar</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>N vägskärningen, S Tvärvägen O om Mossvägen, Vg</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>413476</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6446513</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Luttra</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2016-07-03</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2016-07-03</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>3 ex i O, inte noterade tidigare</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>119338954</v>
+      </c>
+      <c r="B49" t="n">
+        <v>108201</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220107</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Klofibbla</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Crepis tectorum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Mossvägen: O vägkant vid Hulesjön, Vg</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>413563</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6446764</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>några blommande ex, bl a ett stort med rätt brett tunglika blad. Inte noga nycklad, men grönfibbla var det i alla fall inte.</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>60510365</v>
+      </c>
+      <c r="B50" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>N vägskärningen, S Tvärvägen O om Mossvägen, Vg</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>413476</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6446513</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Luttra</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2016-07-03</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2016-07-03</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>en stor tuva ovanför det största området naken skiffer</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2710933</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>SO om Hulesjön, infarten mot fd ladan, Vg</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>413492</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6446691</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2012-01-16</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2012-01-16</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>6981261</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Mossvägen, O vägkant S om Hulesjön, Vg</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>413484</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6446684</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Luttra</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2013-06-14</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2013-06-14</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>68888719</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Hulesjön SO om, Vg</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>413509</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6446621</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Luttra</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2017-02-25</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2017-02-25</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Vändplats, vägdike och vägkant</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>104408831</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Hulesjön, SO om, Vg</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>413491</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6446684</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Luttra</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Ulf Persson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Ulf Persson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>81215724</v>
+      </c>
+      <c r="B55" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Falköpings kommun, Vg</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>413722</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6446493</v>
+      </c>
+      <c r="S55" t="n">
+        <v>25</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Luttra</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2018-06-15</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2018-08-15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Observatör: Lennart Sundh. Naturvärdesinventering för Falköpings kommun. Calluna AB (JSN0108).</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Erik Edvardsson, Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering av kommunal mark i Falköpings kommun 2018-2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>5145134</v>
+      </c>
+      <c r="B56" t="n">
+        <v>100798</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222617</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Flentimotej</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Phleum phleoides</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) H. Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>norra vägskärningen av Södra Tvärvägen O om Mossvägen, Vg</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>413466</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6446513</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Luttra</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2010-08-21</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2010-08-21</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>flera fina tuvor</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>60510220</v>
+      </c>
+      <c r="B57" t="n">
+        <v>100798</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>222617</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Flentimotej</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Phleum phleoides</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) H. Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>N vägskärningen, S Tvärvägen O om Mossvägen, Vg</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>413496</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6446503</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Luttra</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2016-06-25</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2016-06-25</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>talrik blommande, alla kortväxta</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>134145363</v>
+      </c>
+      <c r="B58" t="n">
+        <v>103482</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Falevi, Vg</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>413493</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6446678</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Luttra</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>5893253</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99029</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>223578</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Äkta ängsnycklar</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata var. incarnata</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Södra Tvärvägen SO om Hulesjön, Vg</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>413463</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6446512</v>
+      </c>
+      <c r="S59" t="n">
+        <v>25</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Luttra</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2003-06-26</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2003-06-26</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>2 ex</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>5901890</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99029</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>223578</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Äkta ängsnycklar</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata var. incarnata</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>norra vägskärningen av Södra Tvärvägen O om Mossvägen, Vg</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>413466</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6446513</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Luttra</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2010-08-21</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2010-08-21</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>22 eller något fler nere i vägdiket</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Jörgen Grahn</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50775-2025 artfynd.xlsx
+++ b/artfynd/A 50775-2025 artfynd.xlsx
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+          <t>Enviro Planning, Sofia Berg, Alfred Olofsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+          <t>Enviro Planning, Sofia Berg, Alfred Olofsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+          <t>Enviro Planning, Sofia Berg, Alfred Olofsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 50775-2025 artfynd.xlsx
+++ b/artfynd/A 50775-2025 artfynd.xlsx
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Enviro Planning, Sofia Berg, Alfred Olofsson</t>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Enviro Planning, Sofia Berg, Alfred Olofsson</t>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Enviro Planning, Sofia Berg, Alfred Olofsson</t>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
